--- a/app/reports/PIAC_research.xlsx
+++ b/app/reports/PIAC_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -151,6 +151,8 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -618,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-05-31 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -687,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -862,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0445300006866455</v>
+        <v>0.0447700023651123</v>
       </c>
     </row>
     <row r="6">
@@ -1191,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>120486058.8235294</v>
+        <v>120486050</v>
       </c>
     </row>
     <row r="36">
@@ -1212,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="38">
@@ -1417,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1491,62 +1493,226 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>6144789</v>
+        <v>7229163</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>
       <c r="F5" s="31" t="n"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BGTTF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GOAT INDS LTD.</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>10470998</v>
+      </c>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ESIFF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AI ARTIFICIAL INTELLIGENCE VENT</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>5124072</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>5.3333335</v>
+      </c>
+      <c r="E7" s="33" t="n"/>
+      <c r="F7" s="33" t="n">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EWGFF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EAT WELL INVT GROUP INC</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>21439338</v>
+      </c>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n">
+        <v>8.909000000000001</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>0.624</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IHLDF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Immutable Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>4708372</v>
+      </c>
+      <c r="D9" s="33" t="n"/>
+      <c r="E9" s="33" t="n">
+        <v>-0.784</v>
+      </c>
+      <c r="F9" s="33" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ITPC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Intrepid Capital Corp.</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>5395250</v>
+      </c>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n">
+        <v>4.059</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>0.522</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MVNT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MOVEMENT INDS CORP.</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>5200774</v>
+      </c>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="n"/>
+      <c r="F11" s="33" t="n">
+        <v>4.175</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ORLCF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ORACLE COMMODITY HLDG CORP</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>2885186</v>
+      </c>
+      <c r="D12" s="33" t="n"/>
+      <c r="E12" s="33" t="n"/>
+      <c r="F12" s="33" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PNXPF</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Planet Ventures Inc</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>36023804</v>
+      </c>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="33" t="n">
+        <v>-5.112</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>-6.201</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D7" s="32">
-        <f>MEDIAN(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>MEDIAN(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>MEDIAN(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D15" s="34">
+        <f>MEDIAN(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="34">
+        <f>MEDIAN(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="34">
+        <f>MEDIAN(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D8" s="32">
-        <f>AVERAGE(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>AVERAGE(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F8" s="32">
-        <f>AVERAGE(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D16" s="34">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="34">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="34">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/PIAC_research.xlsx
+++ b/app/reports/PIAC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-02 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.06</v>
+        <v>0.051</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0447700023651123</v>
+        <v>0.04456999778747558</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>120486050</v>
+        <v>120486058.8235294</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.06</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="38">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>7229163</v>
+        <v>6144789</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>10470998</v>
+        <v>8444353</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n"/>
@@ -1529,14 +1529,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>5124072</v>
+        <v>5444327</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>5.3333335</v>
+        <v>5.666667</v>
       </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n">
-        <v>7.87</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="8">
@@ -1551,14 +1551,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>21439338</v>
+        <v>7146446</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>8.909000000000001</v>
+        <v>10.284</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>0.624</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="9">
@@ -1573,11 +1573,11 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>4708372</v>
+        <v>4453335</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-0.784</v>
+        <v>-0.548</v>
       </c>
       <c r="F9" s="33" t="n"/>
     </row>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>5200774</v>
+        <v>5778638</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n"/>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>2885186</v>
+        <v>2766115</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
@@ -1653,14 +1653,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>36023804</v>
+        <v>36495196</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-5.112</v>
+        <v>-5.129</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-6.201</v>
+        <v>-6.221</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/PIAC_research.xlsx
+++ b/app/reports/PIAC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-02 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-03 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04456999778747558</v>
+        <v>0.04497000217437744</v>
       </c>
     </row>
     <row r="6">
@@ -1529,14 +1529,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>5444327</v>
+        <v>5764581</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>5.666667</v>
+        <v>6.0000005</v>
       </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n">
-        <v>7.35</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="8">
@@ -1555,10 +1555,10 @@
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>10.284</v>
+        <v>14.623</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>0.721</v>
+        <v>0.766</v>
       </c>
     </row>
     <row r="9">
@@ -1573,11 +1573,11 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>4453335</v>
+        <v>4526903</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-0.548</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="F9" s="33" t="n"/>
     </row>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>5778638</v>
+        <v>2923311</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n"/>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>2766115</v>
+        <v>2942432</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
@@ -1653,14 +1653,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>36495196</v>
+        <v>34396724</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-5.129</v>
+        <v>-4.844</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-6.221</v>
+        <v>-5.876</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/PIAC_research.xlsx
+++ b/app/reports/PIAC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-03 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-04 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04497000217437744</v>
+        <v>0.04470999717712403</v>
       </c>
     </row>
     <row r="6">
@@ -1529,14 +1529,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>5764581</v>
+        <v>5136882</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>6.0000005</v>
+        <v>5.346667</v>
       </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n">
-        <v>7.88</v>
+        <v>7.361</v>
       </c>
     </row>
     <row r="8">
@@ -1551,14 +1551,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>7146446</v>
+        <v>4466529</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>14.623</v>
+        <v>13.614</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>0.766</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="9">
@@ -1615,12 +1615,12 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>2923311</v>
+        <v>4248998</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n">
-        <v>4.175</v>
+        <v>3.142</v>
       </c>
     </row>
     <row r="12">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>2942432</v>
+        <v>2518813</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
@@ -1653,14 +1653,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>34396724</v>
+        <v>34214248</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-4.844</v>
+        <v>-4.689</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-5.876</v>
+        <v>-5.687</v>
       </c>
     </row>
     <row r="15">
